--- a/per-stock/NRG/financials.xlsx
+++ b/per-stock/NRG/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26966179840</v>
+        <v>28495831040</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>50796179456</v>
+        <v>52325830656</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>140.45055</v>
+        <v>150.06667</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11.198446</v>
+        <v>11.621393</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8327007</v>
+        <v>0.8799355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>431624992</v>
+        <v>-356000000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>127.81</v>
+        <v>135.06</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D52</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C52</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B52</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B47:E47)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D50</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C50</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B50</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B45:E45)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D43</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C43</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B43</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B40:E40)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B7:E7)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B5</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1858,7 +2338,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1925,7 +2405,9 @@
           <t>Tax Effect Of Unusual Items</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
+      <c r="B2" s="3" t="n">
+        <v>-18000000</v>
+      </c>
       <c r="C2" s="3" t="n">
         <v>-15120000</v>
       </c>
@@ -1938,9 +2420,7 @@
       <c r="F2" s="3" t="n">
         <v>-3585000</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>-16011188.811189</v>
-      </c>
+      <c r="G2" s="3" t="n"/>
       <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
@@ -1949,7 +2429,9 @@
           <t>Tax Rate For Calcs</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
+      <c r="B3" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="C3" s="3" t="n">
         <v>0.21</v>
       </c>
@@ -1962,9 +2444,7 @@
       <c r="F3" s="3" t="n">
         <v>0.239</v>
       </c>
-      <c r="G3" s="3" t="n">
-        <v>0.100699</v>
-      </c>
+      <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
@@ -1973,7 +2453,9 @@
           <t>Normalized EBITDA</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
+      <c r="B4" s="3" t="n">
+        <v>845000000</v>
+      </c>
       <c r="C4" s="3" t="n">
         <v>755000000</v>
       </c>
@@ -1986,9 +2468,7 @@
       <c r="F4" s="3" t="n">
         <v>1489000000</v>
       </c>
-      <c r="G4" s="3" t="n">
-        <v>1355000000</v>
-      </c>
+      <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
@@ -1997,7 +2477,9 @@
           <t>Total Unusual Items</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
+      <c r="B5" s="3" t="n">
+        <v>-45000000</v>
+      </c>
       <c r="C5" s="3" t="n">
         <v>-72000000</v>
       </c>
@@ -2010,9 +2492,7 @@
       <c r="F5" s="3" t="n">
         <v>-15000000</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>-159000000</v>
-      </c>
+      <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
@@ -2021,7 +2501,9 @@
           <t>Total Unusual Items Excluding Goodwill</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
+      <c r="B6" s="3" t="n">
+        <v>-45000000</v>
+      </c>
       <c r="C6" s="3" t="n">
         <v>-72000000</v>
       </c>
@@ -2034,9 +2516,7 @@
       <c r="F6" s="3" t="n">
         <v>-15000000</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>-159000000</v>
-      </c>
+      <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
@@ -2045,7 +2525,9 @@
           <t>Net Income From Continuing Operation Net Minority Interest</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
+      <c r="B7" s="3" t="n">
+        <v>125000000</v>
+      </c>
       <c r="C7" s="3" t="n">
         <v>66000000</v>
       </c>
@@ -2058,9 +2540,7 @@
       <c r="F7" s="3" t="n">
         <v>750000000</v>
       </c>
-      <c r="G7" s="3" t="n">
-        <v>643000000</v>
-      </c>
+      <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
@@ -2069,7 +2549,9 @@
           <t>Reconciled Depreciation</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
+      <c r="B8" s="3" t="n">
+        <v>277000000</v>
+      </c>
       <c r="C8" s="3" t="n">
         <v>229000000</v>
       </c>
@@ -2082,9 +2564,7 @@
       <c r="F8" s="3" t="n">
         <v>218000000</v>
       </c>
-      <c r="G8" s="3" t="n">
-        <v>257000000</v>
-      </c>
+      <c r="G8" s="3" t="n"/>
       <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
@@ -2093,7 +2573,9 @@
           <t>Reconciled Cost Of Revenue</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n"/>
+      <c r="B9" s="3" t="n">
+        <v>9013000000</v>
+      </c>
       <c r="C9" s="3" t="n">
         <v>6477000000</v>
       </c>
@@ -2106,9 +2588,7 @@
       <c r="F9" s="3" t="n">
         <v>6669000000</v>
       </c>
-      <c r="G9" s="3" t="n">
-        <v>4972000000</v>
-      </c>
+      <c r="G9" s="3" t="n"/>
       <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
@@ -2117,7 +2597,9 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n"/>
+      <c r="B10" s="3" t="n">
+        <v>800000000</v>
+      </c>
       <c r="C10" s="3" t="n">
         <v>683000000</v>
       </c>
@@ -2130,9 +2612,7 @@
       <c r="F10" s="3" t="n">
         <v>1474000000</v>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>1196000000</v>
-      </c>
+      <c r="G10" s="3" t="n"/>
       <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
@@ -2141,7 +2621,9 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
+      <c r="B11" s="3" t="n">
+        <v>368000000</v>
+      </c>
       <c r="C11" s="3" t="n">
         <v>307000000</v>
       </c>
@@ -2154,9 +2636,7 @@
       <c r="F11" s="3" t="n">
         <v>1148000000</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>838000000</v>
-      </c>
+      <c r="G11" s="3" t="n"/>
       <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
@@ -2165,7 +2645,9 @@
           <t>Net Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
+      <c r="B12" s="3" t="n">
+        <v>-285000000</v>
+      </c>
       <c r="C12" s="3" t="n">
         <v>-243000000</v>
       </c>
@@ -2178,9 +2660,7 @@
       <c r="F12" s="3" t="n">
         <v>-163000000</v>
       </c>
-      <c r="G12" s="3" t="n">
-        <v>-123000000</v>
-      </c>
+      <c r="G12" s="3" t="n"/>
       <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
@@ -2189,7 +2669,9 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
+      <c r="B13" s="3" t="n">
+        <v>285000000</v>
+      </c>
       <c r="C13" s="3" t="n">
         <v>243000000</v>
       </c>
@@ -2202,9 +2684,7 @@
       <c r="F13" s="3" t="n">
         <v>163000000</v>
       </c>
-      <c r="G13" s="3" t="n">
-        <v>123000000</v>
-      </c>
+      <c r="G13" s="3" t="n"/>
       <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
@@ -2213,7 +2693,9 @@
           <t>Normalized Income</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
+      <c r="B14" s="3" t="n">
+        <v>152000000</v>
+      </c>
       <c r="C14" s="3" t="n">
         <v>122880000</v>
       </c>
@@ -2226,9 +2708,7 @@
       <c r="F14" s="3" t="n">
         <v>761415000</v>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>785988811.1888109</v>
-      </c>
+      <c r="G14" s="3" t="n"/>
       <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
@@ -2237,7 +2717,9 @@
           <t>Net Income From Continuing And Discontinued Operation</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
+      <c r="B15" s="3" t="n">
+        <v>125000000</v>
+      </c>
       <c r="C15" s="3" t="n">
         <v>66000000</v>
       </c>
@@ -2250,9 +2732,7 @@
       <c r="F15" s="3" t="n">
         <v>750000000</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>643000000</v>
-      </c>
+      <c r="G15" s="3" t="n"/>
       <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
@@ -2261,7 +2741,9 @@
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
+      <c r="B16" s="3" t="n">
+        <v>9883000000</v>
+      </c>
       <c r="C16" s="3" t="n">
         <v>7423000000</v>
       </c>
@@ -2274,9 +2756,7 @@
       <c r="F16" s="3" t="n">
         <v>7436000000</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>5835000000</v>
-      </c>
+      <c r="G16" s="3" t="n"/>
       <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
@@ -2285,7 +2765,9 @@
           <t>Total Operating Income As Reported</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
+      <c r="B17" s="3" t="n">
+        <v>328000000</v>
+      </c>
       <c r="C17" s="3" t="n">
         <v>297000000</v>
       </c>
@@ -2298,9 +2780,7 @@
       <c r="F17" s="3" t="n">
         <v>1134000000</v>
       </c>
-      <c r="G17" s="3" t="n">
-        <v>954000000</v>
-      </c>
+      <c r="G17" s="3" t="n"/>
       <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
@@ -2405,7 +2885,9 @@
           <t>Diluted NI Availto Com Stockholders</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n"/>
+      <c r="B22" s="3" t="n">
+        <v>108000000</v>
+      </c>
       <c r="C22" s="3" t="n">
         <v>50000000</v>
       </c>
@@ -2418,9 +2900,7 @@
       <c r="F22" s="3" t="n">
         <v>733000000</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>627000000</v>
-      </c>
+      <c r="G22" s="3" t="n"/>
       <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
@@ -2429,7 +2909,9 @@
           <t>Net Income Common Stockholders</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n"/>
+      <c r="B23" s="3" t="n">
+        <v>108000000</v>
+      </c>
       <c r="C23" s="3" t="n">
         <v>50000000</v>
       </c>
@@ -2442,9 +2924,7 @@
       <c r="F23" s="3" t="n">
         <v>733000000</v>
       </c>
-      <c r="G23" s="3" t="n">
-        <v>627000000</v>
-      </c>
+      <c r="G23" s="3" t="n"/>
       <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
@@ -2453,7 +2933,9 @@
           <t>Preferred Stock Dividends</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
+      <c r="B24" s="3" t="n">
+        <v>17000000</v>
+      </c>
       <c r="C24" s="3" t="n">
         <v>16000000</v>
       </c>
@@ -2466,9 +2948,7 @@
       <c r="F24" s="3" t="n">
         <v>17000000</v>
       </c>
-      <c r="G24" s="3" t="n">
-        <v>16000000</v>
-      </c>
+      <c r="G24" s="3" t="n"/>
       <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
@@ -2477,7 +2957,9 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n"/>
+      <c r="B25" s="3" t="n">
+        <v>125000000</v>
+      </c>
       <c r="C25" s="3" t="n">
         <v>66000000</v>
       </c>
@@ -2490,9 +2972,7 @@
       <c r="F25" s="3" t="n">
         <v>750000000</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>643000000</v>
-      </c>
+      <c r="G25" s="3" t="n"/>
       <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
@@ -2501,7 +2981,9 @@
           <t>Net Income Including Noncontrolling Interests</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n"/>
+      <c r="B26" s="3" t="n">
+        <v>125000000</v>
+      </c>
       <c r="C26" s="3" t="n">
         <v>66000000</v>
       </c>
@@ -2514,9 +2996,7 @@
       <c r="F26" s="3" t="n">
         <v>750000000</v>
       </c>
-      <c r="G26" s="3" t="n">
-        <v>643000000</v>
-      </c>
+      <c r="G26" s="3" t="n"/>
       <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
@@ -2525,7 +3005,9 @@
           <t>Net Income Continuous Operations</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n"/>
+      <c r="B27" s="3" t="n">
+        <v>125000000</v>
+      </c>
       <c r="C27" s="3" t="n">
         <v>66000000</v>
       </c>
@@ -2538,9 +3020,7 @@
       <c r="F27" s="3" t="n">
         <v>750000000</v>
       </c>
-      <c r="G27" s="3" t="n">
-        <v>643000000</v>
-      </c>
+      <c r="G27" s="3" t="n"/>
       <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
@@ -2549,7 +3029,9 @@
           <t>Tax Provision</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n"/>
+      <c r="B28" s="3" t="n">
+        <v>-42000000</v>
+      </c>
       <c r="C28" s="3" t="n">
         <v>-2000000</v>
       </c>
@@ -2562,9 +3044,7 @@
       <c r="F28" s="3" t="n">
         <v>235000000</v>
       </c>
-      <c r="G28" s="3" t="n">
-        <v>72000000</v>
-      </c>
+      <c r="G28" s="3" t="n"/>
       <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
@@ -2573,7 +3053,9 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n"/>
+      <c r="B29" s="3" t="n">
+        <v>83000000</v>
+      </c>
       <c r="C29" s="3" t="n">
         <v>64000000</v>
       </c>
@@ -2586,9 +3068,7 @@
       <c r="F29" s="3" t="n">
         <v>985000000</v>
       </c>
-      <c r="G29" s="3" t="n">
-        <v>715000000</v>
-      </c>
+      <c r="G29" s="3" t="n"/>
       <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
@@ -2597,7 +3077,9 @@
           <t>Other Income Expense</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n"/>
+      <c r="B30" s="3" t="n">
+        <v>-5000000</v>
+      </c>
       <c r="C30" s="3" t="n">
         <v>-23000000</v>
       </c>
@@ -2610,9 +3092,7 @@
       <c r="F30" s="3" t="n">
         <v>-1000000</v>
       </c>
-      <c r="G30" s="3" t="n">
-        <v>-146000000</v>
-      </c>
+      <c r="G30" s="3" t="n"/>
       <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
@@ -2621,7 +3101,9 @@
           <t>Other Non Operating Income Expenses</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n"/>
+      <c r="B31" s="3" t="n">
+        <v>40000000</v>
+      </c>
       <c r="C31" s="3" t="n">
         <v>42000000</v>
       </c>
@@ -2632,11 +3114,9 @@
         <v>4000000</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>6000000</v>
-      </c>
+        <v>14000000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
       <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
@@ -2645,7 +3125,9 @@
           <t>Special Income Charges</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n"/>
+      <c r="B32" s="3" t="n">
+        <v>-45000000</v>
+      </c>
       <c r="C32" s="3" t="n">
         <v>-72000000</v>
       </c>
@@ -2658,9 +3140,7 @@
       <c r="F32" s="3" t="n">
         <v>-15000000</v>
       </c>
-      <c r="G32" s="3" t="n">
-        <v>-159000000</v>
-      </c>
+      <c r="G32" s="3" t="n"/>
       <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
@@ -2669,7 +3149,9 @@
           <t>Gain On Sale Of Ppe</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n"/>
+      <c r="B33" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="C33" s="3" t="n">
         <v>-18000000</v>
       </c>
@@ -2682,9 +3164,7 @@
       <c r="F33" s="3" t="n">
         <v>-7000000</v>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>-1000000</v>
-      </c>
+      <c r="G33" s="3" t="n"/>
       <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
@@ -2737,7 +3217,9 @@
           <t>Restructuring And Mergern Acquisition</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n"/>
+      <c r="B36" s="3" t="n">
+        <v>45000000</v>
+      </c>
       <c r="C36" s="3" t="n">
         <v>15000000</v>
       </c>
@@ -2750,9 +3232,7 @@
       <c r="F36" s="3" t="n">
         <v>8000000</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>8000000</v>
-      </c>
+      <c r="G36" s="3" t="n"/>
       <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
@@ -2785,7 +3265,9 @@
           <t>Net Non Operating Interest Income Expense</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n"/>
+      <c r="B38" s="3" t="n">
+        <v>-285000000</v>
+      </c>
       <c r="C38" s="3" t="n">
         <v>-243000000</v>
       </c>
@@ -2798,9 +3280,7 @@
       <c r="F38" s="3" t="n">
         <v>-163000000</v>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>-123000000</v>
-      </c>
+      <c r="G38" s="3" t="n"/>
       <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
@@ -2809,7 +3289,9 @@
           <t>Interest Expense Non Operating</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n"/>
+      <c r="B39" s="3" t="n">
+        <v>285000000</v>
+      </c>
       <c r="C39" s="3" t="n">
         <v>243000000</v>
       </c>
@@ -2822,9 +3304,7 @@
       <c r="F39" s="3" t="n">
         <v>163000000</v>
       </c>
-      <c r="G39" s="3" t="n">
-        <v>123000000</v>
-      </c>
+      <c r="G39" s="3" t="n"/>
       <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
@@ -2833,7 +3313,9 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n"/>
+      <c r="B40" s="3" t="n">
+        <v>373000000</v>
+      </c>
       <c r="C40" s="3" t="n">
         <v>330000000</v>
       </c>
@@ -2846,9 +3328,7 @@
       <c r="F40" s="3" t="n">
         <v>1149000000</v>
       </c>
-      <c r="G40" s="3" t="n">
-        <v>984000000</v>
-      </c>
+      <c r="G40" s="3" t="n"/>
       <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
@@ -2857,7 +3337,9 @@
           <t>Operating Expense</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n"/>
+      <c r="B41" s="3" t="n">
+        <v>1025000000</v>
+      </c>
       <c r="C41" s="3" t="n">
         <v>1093000000</v>
       </c>
@@ -2870,9 +3352,7 @@
       <c r="F41" s="3" t="n">
         <v>875000000</v>
       </c>
-      <c r="G41" s="3" t="n">
-        <v>964000000</v>
-      </c>
+      <c r="G41" s="3" t="n"/>
       <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
@@ -2881,7 +3361,9 @@
           <t>Depreciation Amortization Depletion Income Statement</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n"/>
+      <c r="B42" s="3" t="n">
+        <v>432000000</v>
+      </c>
       <c r="C42" s="3" t="n">
         <v>376000000</v>
       </c>
@@ -2894,9 +3376,7 @@
       <c r="F42" s="3" t="n">
         <v>326000000</v>
       </c>
-      <c r="G42" s="3" t="n">
-        <v>358000000</v>
-      </c>
+      <c r="G42" s="3" t="n"/>
       <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
@@ -2905,7 +3385,9 @@
           <t>Depreciation And Amortization In Income Statement</t>
         </is>
       </c>
-      <c r="B43" s="3" t="n"/>
+      <c r="B43" s="3" t="n">
+        <v>432000000</v>
+      </c>
       <c r="C43" s="3" t="n">
         <v>376000000</v>
       </c>
@@ -2918,9 +3400,7 @@
       <c r="F43" s="3" t="n">
         <v>326000000</v>
       </c>
-      <c r="G43" s="3" t="n">
-        <v>358000000</v>
-      </c>
+      <c r="G43" s="3" t="n"/>
       <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
@@ -2929,7 +3409,9 @@
           <t>Selling General And Administration</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n"/>
+      <c r="B44" s="3" t="n">
+        <v>593000000</v>
+      </c>
       <c r="C44" s="3" t="n">
         <v>717000000</v>
       </c>
@@ -2942,9 +3424,7 @@
       <c r="F44" s="3" t="n">
         <v>549000000</v>
       </c>
-      <c r="G44" s="3" t="n">
-        <v>292000000</v>
-      </c>
+      <c r="G44" s="3" t="n"/>
       <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
@@ -2953,7 +3433,9 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n"/>
+      <c r="B45" s="3" t="n">
+        <v>1398000000</v>
+      </c>
       <c r="C45" s="3" t="n">
         <v>1423000000</v>
       </c>
@@ -2966,9 +3448,7 @@
       <c r="F45" s="3" t="n">
         <v>2024000000</v>
       </c>
-      <c r="G45" s="3" t="n">
-        <v>1948000000</v>
-      </c>
+      <c r="G45" s="3" t="n"/>
       <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
@@ -2977,7 +3457,9 @@
           <t>Cost Of Revenue</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n"/>
+      <c r="B46" s="3" t="n">
+        <v>8858000000</v>
+      </c>
       <c r="C46" s="3" t="n">
         <v>6330000000</v>
       </c>
@@ -2990,9 +3472,7 @@
       <c r="F46" s="3" t="n">
         <v>6561000000</v>
       </c>
-      <c r="G46" s="3" t="n">
-        <v>4871000000</v>
-      </c>
+      <c r="G46" s="3" t="n"/>
       <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
@@ -3001,7 +3481,9 @@
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n"/>
+      <c r="B47" s="3" t="n">
+        <v>10256000000</v>
+      </c>
       <c r="C47" s="3" t="n">
         <v>7753000000</v>
       </c>
@@ -3014,9 +3496,7 @@
       <c r="F47" s="3" t="n">
         <v>8585000000</v>
       </c>
-      <c r="G47" s="3" t="n">
-        <v>6819000000</v>
-      </c>
+      <c r="G47" s="3" t="n"/>
       <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
@@ -3025,7 +3505,9 @@
           <t>Operating Revenue</t>
         </is>
       </c>
-      <c r="B48" s="3" t="n"/>
+      <c r="B48" s="3" t="n">
+        <v>10172000000</v>
+      </c>
       <c r="C48" s="3" t="n">
         <v>7703000000</v>
       </c>
@@ -3038,9 +3520,7 @@
       <c r="F48" s="3" t="n">
         <v>8493000000</v>
       </c>
-      <c r="G48" s="3" t="n">
-        <v>6741000000</v>
-      </c>
+      <c r="G48" s="3" t="n"/>
       <c r="H48" s="3" t="n"/>
     </row>
   </sheetData>
@@ -3048,7 +3528,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4652,7 +5132,1751 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>12087277</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>9452008</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>7448883</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>6457685</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>6599095</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>212762887</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>190376607</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>192255304</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>194630094</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>196462125</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>224850164</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>199828615</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>199704187</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>201087779</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>203061220</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>22976000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>11735000000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>11200000000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>10764000000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>10116000000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>23357000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>16622000000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>12111000000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>11116000000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>10986000000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>-7119000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>-6295000000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>-6126000000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-5888000000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>-5735000000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>27378000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>17474000000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>13252000000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>12582000000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>12936000000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>-1925000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>5118000000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>411000000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-586000000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>575000000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>-6469000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>-5645000000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>-5476000000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>-5238000000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>-5085000000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>203000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>179000000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>179000000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>172000000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>177000000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>4224000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1031000000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>1320000000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>1638000000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>2127000000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Preferred Stock Equity</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>650000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>650000000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>650000000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>650000000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>650000000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>24653000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>18093000000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>13125000000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>12100000000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>12589000000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>4874000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>1681000000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1970000000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>2288000000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>2777000000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>4874000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>1681000000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1970000000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>2288000000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>2777000000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-84000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-81000000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-105000000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-101000000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-115000000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>-84000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>-81000000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>-105000000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-101000000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>-115000000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>1531000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>1087000000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>745000000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>538000000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>440000000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1969000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1982000000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2002000000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>1970000000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>2162000000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>3868000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>215000000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>166000000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>305000000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>518000000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>652000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>652000000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>652000000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>652000000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>652000000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>650000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>650000000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>650000000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>650000000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>650000000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>35179000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>27459000000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>22001000000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>21800000000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>22214000000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>23332000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>19430000000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>14288000000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>13019000000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>12914000000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>920000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>861000000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>911000000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>883000000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>847000000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Derivative Product Liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1461000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1103000000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1125000000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>1273000000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>1288000000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>1007000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>910000000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>954000000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>917000000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>842000000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>868000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>895000000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>942000000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>905000000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>830000000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>139000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>19944000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>16556000000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>11298000000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>9946000000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>9937000000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>165000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>144000000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>143000000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>134000000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>125000000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>19779000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>16412000000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>11155000000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>9812000000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>9812000000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>11847000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>8029000000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>7713000000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>8781000000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>9300000000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>3406000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>3325000000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>2203000000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>2400000000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>3325000000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>727000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>748000000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>710000000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>715000000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>690000000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>727000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>748000000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>710000000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>715000000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>690000000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>3413000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>66000000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>813000000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>1170000000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>1049000000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>3375000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>31000000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>777000000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>1132000000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>997000000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>3375000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>31000000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>777000000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>1132000000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>997000000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n"/>
+      <c r="C43" s="3" t="n">
+        <v>561000000</v>
+      </c>
+      <c r="D43" s="3" t="n"/>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="n"/>
+      <c r="G43" s="3" t="n">
+        <v>514000000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>4301000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>3329000000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>3987000000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>4496000000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>4236000000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>1816000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>495000000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>1668000000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>1952000000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>1880000000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>2485000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>2834000000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>2319000000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>2544000000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>2356000000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>2485000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>2834000000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>2319000000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>2544000000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>2356000000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>40053000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>29140000000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>23971000000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>24088000000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>24991000000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>30131000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>15993000000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>15847000000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>15893000000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>15116000000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>1602000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>1478000000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>1477000000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>1315000000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>1186000000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>1796000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>1843000000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>1855000000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>1935000000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1923000000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>1796000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>1843000000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>1855000000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>1935000000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>1923000000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Financial Assets</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>1704000000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>1568000000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>1486000000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>1745000000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>1735000000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n"/>
+      <c r="C54" s="3" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>45000000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Long Term Equity Investment</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n"/>
+      <c r="C55" s="3" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>45000000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>11343000000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>7326000000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>7446000000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>7526000000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>7862000000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>2462000000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>2309000000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>2431000000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>2509000000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>2850000000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>8881000000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>5017000000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>5015000000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>5017000000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>5012000000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>13686000000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>3762000000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>3535000000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>3325000000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>2363000000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n"/>
+      <c r="C60" s="3" t="n">
+        <v>-1774000000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>-1702000000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>-1632000000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>-1569000000</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>-1508000000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>13686000000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>5536000000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>5237000000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>4957000000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>3932000000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n"/>
+      <c r="C62" s="3" t="n">
+        <v>1196000000</v>
+      </c>
+      <c r="D62" s="3" t="n"/>
+      <c r="E62" s="3" t="n"/>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3" t="n">
+        <v>442000000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>13686000000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>4340000000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>5237000000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>4957000000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>3932000000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>9922000000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>13147000000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>8124000000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>8195000000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>9875000000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>1382000000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>1069000000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>969000000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>987000000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>899000000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Hedging Assets Current</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>3081000000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>2189000000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>1928000000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>2332000000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>3436000000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Restricted Cash</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>839000000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>655000000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>711000000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>824000000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>962000000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>665000000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>461000000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>452000000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>451000000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>373000000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Other Inventories</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n"/>
+      <c r="C69" s="3" t="n">
+        <v>73000000</v>
+      </c>
+      <c r="D69" s="3" t="n"/>
+      <c r="E69" s="3" t="n"/>
+      <c r="F69" s="3" t="n"/>
+      <c r="G69" s="3" t="n">
+        <v>79000000</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>3777000000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>4065000000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>3332000000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>3421000000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>3512000000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>3777000000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>4065000000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>3332000000</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>3421000000</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>3512000000</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>-150000000</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>-146000000</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>-164000000</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>-127000000</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>-144000000</v>
+      </c>
+      <c r="G72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>3927000000</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>4211000000</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>3496000000</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>3548000000</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>3656000000</v>
+      </c>
+      <c r="G73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>178000000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>4708000000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>732000000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>180000000</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>693000000</v>
+      </c>
+      <c r="G74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>178000000</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>4708000000</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>732000000</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>180000000</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>693000000</v>
+      </c>
+      <c r="G75" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6094,13 +8318,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6110,6 +8334,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6120,30 +8345,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -6156,21 +8386,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-486000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-170000000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>231000000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>69000000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>635000000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>764000000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6179,21 +8410,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-560000000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>-359000000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>-364000000</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>-326000000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-354000000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>-624000000</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6202,21 +8434,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-1537000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-756000000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-1084000000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-735000000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-5000000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-2295000000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6225,21 +8458,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>4907000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>5301000000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>2085000000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>865000000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>2325000000</v>
-      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6251,12 +8485,13 @@
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6265,21 +8500,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-317000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-293000000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-253000000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-382000000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-220000000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>-188000000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6288,21 +8524,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>411000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>4998000000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>1085000000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>643000000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>1438000000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>1173000000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6311,21 +8548,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>4998000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>1085000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>643000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>1438000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>1173000000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>1126000000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6337,18 +8575,19 @@
         <v>2000000</v>
       </c>
       <c r="C10" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D10" s="3" t="n">
         <v>1000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>-1000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>-4000000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6357,21 +8596,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-4589000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>3911000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>441000000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-794000000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>263000000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>51000000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6380,21 +8620,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>2652000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>4086000000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>215000000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-297000000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-458000000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-714000000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6403,21 +8644,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>2652000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>4086000000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>215000000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>-297000000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>-458000000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>-714000000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6426,21 +8668,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-23000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-15000000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-303000000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-15000000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>22000000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>-37000000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6449,21 +8692,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-135000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-85000000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-119000000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-86000000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-121000000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>-83000000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6475,10 +8719,11 @@
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n">
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="H16" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6492,12 +8737,13 @@
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H17" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6506,21 +8752,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-560000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>-359000000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-364000000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>-326000000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-354000000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>-624000000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6529,21 +8776,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>-560000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>-359000000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>-364000000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>-326000000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-354000000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>-624000000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6552,667 +8800,903 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>3370000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>4545000000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>1001000000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>130000000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-5000000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>30000000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Net Long Term Debt Issuance</t>
+          <t>Net Short Term Debt Issuance</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>7125000000</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>1001000000</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>-5000000</v>
-      </c>
+        <v>3325000000</v>
+      </c>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n">
-        <v>4335000000</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Long Term Debt Payments</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n">
-        <v>-1084000000</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>-735000000</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>-5000000</v>
-      </c>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n">
-        <v>-429000000</v>
-      </c>
+          <t>Short Term Debt Payments</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>-1525000000</v>
+      </c>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Long Term Debt Issuance</t>
+          <t>Short Term Debt Issuance</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5301000000</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>2085000000</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>865000000</v>
-      </c>
-      <c r="E23" s="3" t="n">
+        <v>4850000000</v>
+      </c>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>2325000000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Investing Cash Flow</t>
+          <t>Net Long Term Debt Issuance</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-298000000</v>
+        <v>45000000</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>-258000000</v>
+        <v>7125000000</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>-948000000</v>
+        <v>1001000000</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>-134000000</v>
+        <v>130000000</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-187000000</v>
+        <v>-5000000</v>
       </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Investing Activities</t>
+          <t>Long Term Debt Payments</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>-298000000</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>-258000000</v>
-      </c>
+        <v>-12000000</v>
+      </c>
+      <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="n">
-        <v>-948000000</v>
+        <v>-1084000000</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-134000000</v>
+        <v>-735000000</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-187000000</v>
+        <v>-5000000</v>
       </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n">
+        <v>-429000000</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Net Other Investing Changes</t>
+          <t>Long Term Debt Issuance</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>57000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>5301000000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>2085000000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>865000000</v>
+      </c>
+      <c r="F26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>86000000</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>6000000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Net Investment Purchase And Sale</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
+          <t>Investing Cash Flow</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>-7072000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-298000000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-258000000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-948000000</v>
+      </c>
       <c r="F27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-134000000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sale Of Investment</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
+          <t>Cash Flow From Continuing Investing Activities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>-7072000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>-298000000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>-258000000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>-948000000</v>
+      </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-134000000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Purchase Of Investment</t>
+          <t>Net Other Investing Changes</t>
         </is>
       </c>
       <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
+      <c r="C29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="F29" s="3" t="n">
-        <v>0</v>
+        <v>106000000</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>6000000</v>
+      </c>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Net Business Purchase And Sale</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>-5000000</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>-5000000</v>
-      </c>
+          <t>Net Investment Purchase And Sale</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="n"/>
       <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n">
-        <v>-5000000</v>
-      </c>
+      <c r="F30" s="3" t="n"/>
       <c r="G30" s="3" t="n">
-        <v>-1000000</v>
+        <v>0</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Purchase Of Business</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>-5000000</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>-5000000</v>
-      </c>
+          <t>Sale Of Investment</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
       <c r="D31" s="3" t="n"/>
       <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n">
-        <v>-5000000</v>
-      </c>
+      <c r="F31" s="3" t="n"/>
       <c r="G31" s="3" t="n">
-        <v>-1000000</v>
+        <v>0</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Net Intangibles Purchase And Sale</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>-4000000</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>-3000000</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>-2000000</v>
-      </c>
-      <c r="G32" s="3" t="n"/>
+          <t>Purchase Of Investment</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Purchase Of Intangibles</t>
+          <t>Net Business Purchase And Sale</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>5000000</v>
+        <v>-6755000000</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1000000</v>
+        <v>-5000000</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>-4000000</v>
+        <v>-5000000</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-3000000</v>
+        <v>-566000000</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-2000000</v>
+        <v>-20000000</v>
       </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Capital Expenditure Reported</t>
+          <t>Purchase Of Business</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>-298000000</v>
+        <v>-6755000000</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>-254000000</v>
+        <v>-5000000</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>-378000000</v>
+        <v>-5000000</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>-217000000</v>
+        <v>-566000000</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>-186000000</v>
+        <v>-20000000</v>
       </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Operating Cash Flow</t>
+          <t>Net Intangibles Purchase And Sale</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>123000000</v>
+        <v>0</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>484000000</v>
+        <v>5000000</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>451000000</v>
+        <v>1000000</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>855000000</v>
+        <v>-4000000</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>952000000</v>
+        <v>-3000000</v>
       </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cash Flow From Continuing Operating Activities</t>
+          <t>Purchase Of Intangibles</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>123000000</v>
+        <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>484000000</v>
+        <v>5000000</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>451000000</v>
+        <v>1000000</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>855000000</v>
+        <v>-4000000</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>952000000</v>
+        <v>-3000000</v>
       </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Change In Working Capital</t>
+          <t>Capital Expenditure Reported</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>-548000000</v>
+        <v>-317000000</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>-170000000</v>
+        <v>-298000000</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>65000000</v>
+        <v>-254000000</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-253000000</v>
+        <v>-378000000</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>-337000000</v>
+        <v>-217000000</v>
       </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Change In Other Working Capital</t>
+          <t>Operating Cash Flow</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>719000000</v>
+        <v>-169000000</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>-170000000</v>
+        <v>123000000</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>65000000</v>
+        <v>484000000</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>-253000000</v>
+        <v>451000000</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>151000000</v>
+        <v>855000000</v>
       </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Other Non Cash Items</t>
+          <t>Cash Flow From Continuing Operating Activities</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>181000000</v>
+        <v>-169000000</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>150000000</v>
+        <v>123000000</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>155000000</v>
+        <v>484000000</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>4000000</v>
+        <v>451000000</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>113000000</v>
+        <v>855000000</v>
       </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Stock Based Compensation</t>
+          <t>Change In Working Capital</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>51000000</v>
+        <v>-877000000</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>21000000</v>
+        <v>-548000000</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>33000000</v>
+        <v>-170000000</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>29000000</v>
+        <v>66000000</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>20000000</v>
+        <v>-254000000</v>
       </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Provisionand Write Offof Assets</t>
+          <t>Change In Other Working Capital</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>71000000</v>
+        <v>-236000000</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>88000000</v>
+        <v>719000000</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>57000000</v>
+        <v>-170000000</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>56000000</v>
+        <v>-480000000</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>86000000</v>
+        <v>292000000</v>
       </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Asset Impairment Charge</t>
+          <t>Change In Payables And Accrued Expense</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>39000000</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-1225000000</v>
+      </c>
+      <c r="C42" s="3" t="n"/>
       <c r="D42" s="3" t="n"/>
       <c r="E42" s="3" t="n"/>
       <c r="F42" s="3" t="n">
-        <v>28000000</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-381000000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Amortization Of Securities</t>
+          <t>Change In Accrued Expense</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>24000000</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>44000000</v>
-      </c>
+        <v>-315000000</v>
+      </c>
+      <c r="C43" s="3" t="n"/>
+      <c r="D43" s="3" t="n"/>
+      <c r="E43" s="3" t="n"/>
       <c r="F43" s="3" t="n">
-        <v>22000000</v>
+        <v>-185000000</v>
       </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Depreciation Amortization Depletion</t>
+          <t>Change In Payable</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>229000000</v>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>223000000</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>226000000</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>218000000</v>
-      </c>
+        <v>-910000000</v>
+      </c>
+      <c r="C44" s="3" t="n"/>
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n">
-        <v>257000000</v>
+        <v>-196000000</v>
       </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Depreciation And Amortization</t>
+          <t>Change In Account Payable</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>229000000</v>
-      </c>
-      <c r="C45" s="3" t="n">
-        <v>223000000</v>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>226000000</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>218000000</v>
-      </c>
+        <v>-910000000</v>
+      </c>
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="n"/>
       <c r="F45" s="3" t="n">
-        <v>257000000</v>
+        <v>-196000000</v>
       </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Change In Prepaid Assets</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>229000000</v>
+        <v>-196000000</v>
       </c>
       <c r="C46" s="3" t="n"/>
       <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n">
-        <v>218000000</v>
-      </c>
+      <c r="E46" s="3" t="n"/>
       <c r="F46" s="3" t="n">
-        <v>257000000</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>261000000</v>
-      </c>
+        <v>-179000000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Operating Gains Losses</t>
+          <t>Change In Inventory</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>-4000000</v>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>7000000</v>
-      </c>
+        <v>-29000000</v>
+      </c>
+      <c r="C47" s="3" t="n"/>
+      <c r="D47" s="3" t="n"/>
+      <c r="E47" s="3" t="n"/>
       <c r="F47" s="3" t="n">
-        <v>120000000</v>
+        <v>92000000</v>
       </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Earnings Losses From Equity Investments</t>
+          <t>Change In Receivables</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>-6000000</v>
-      </c>
-      <c r="C48" s="3" t="n">
-        <v>-1000000</v>
-      </c>
-      <c r="D48" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>-1000000</v>
-      </c>
+        <v>809000000</v>
+      </c>
+      <c r="C48" s="3" t="n"/>
+      <c r="D48" s="3" t="n"/>
+      <c r="E48" s="3" t="n"/>
       <c r="F48" s="3" t="n">
-        <v>-7000000</v>
+        <v>-78000000</v>
       </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>Changes In Account Receivables</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>809000000</v>
+      </c>
+      <c r="C49" s="3" t="n"/>
+      <c r="D49" s="3" t="n"/>
+      <c r="E49" s="3" t="n"/>
+      <c r="F49" s="3" t="n">
+        <v>-78000000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Other Non Cash Items</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>167000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>181000000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>155000000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Stock Based Compensation</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>41000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>29000000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Provisionand Write Offof Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>59000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>71000000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>88000000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>57000000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>56000000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Asset Impairment Charge</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n"/>
+      <c r="C53" s="3" t="n">
+        <v>39000000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3" t="n"/>
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="3" t="n">
+        <v>28000000</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Amortization Of Securities</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>44000000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Depreciation Amortization Depletion</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>277000000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>229000000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>223000000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>226000000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>218000000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Depreciation And Amortization</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>277000000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>229000000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>223000000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>226000000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>218000000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>277000000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>229000000</v>
+      </c>
+      <c r="D57" s="3" t="n"/>
+      <c r="E57" s="3" t="n"/>
+      <c r="F57" s="3" t="n">
+        <v>218000000</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>257000000</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>261000000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Operating Gains Losses</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>-4000000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Earnings Losses From Equity Investments</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n"/>
+      <c r="C59" s="3" t="n">
+        <v>-6000000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>-7000000</v>
+      </c>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B49" s="3" t="n">
+      <c r="B60" s="3" t="n">
+        <v>125000000</v>
+      </c>
+      <c r="C60" s="3" t="n">
         <v>66000000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D60" s="3" t="n">
         <v>152000000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E60" s="3" t="n">
         <v>-104000000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F60" s="3" t="n">
         <v>750000000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>643000000</v>
-      </c>
-      <c r="G49" s="3" t="n"/>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
